--- a/314e-ig/output/StructureDefinition-clinicalimpression-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-clinicalimpression-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-clinicalimpression-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-clinicalimpression-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-clinicalimpression-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-clinicalimpression-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-clinicalimpression-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-clinicalimpression-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -625,7 +625,7 @@
     <t>ClinicalImpression.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/group-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -647,7 +647,7 @@
     <t>ClinicalImpression.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -710,7 +710,7 @@
     <t>ClinicalImpression.assessor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -732,7 +732,7 @@
     <t>ClinicalImpression.previous</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ClinicalImpression) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/clinicalimpression-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -748,7 +748,7 @@
     <t>ClinicalImpression.problem</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|AllergyIntolerance) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/allergyintolerance-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -842,7 +842,7 @@
     <t>ClinicalImpression.investigation.item</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|FamilyMemberHistory|DiagnosticReport|RiskAssessment|ImagingStudy|Media) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/questionnaireresponse-314e|FamilyMemberHistory|http://314e.com/fhir/StructureDefinition/diagnosticreport-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-lab-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|RiskAssessment|http://314e.com/fhir/StructureDefinition/imagingstudy-314e|http://314e.com/fhir/StructureDefinition/media-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -915,7 +915,7 @@
     <t>ClinicalImpression.finding.itemReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|Media) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/media-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1306,7 +1306,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="152.95703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-clinicalimpression-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-clinicalimpression-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-clinicalimpression-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-clinicalimpression-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
